--- a/estimates/GU_LaLaportFujimi_2413/GU富士見_2413_拾い出し根拠_v2.xlsx
+++ b/estimates/GU_LaLaportFujimi_2413/GU富士見_2413_拾い出し根拠_v2.xlsx
@@ -11,9 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="面積・台数の基本数量" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1からの変更点" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'拾い出し根拠'!$A$4:$H$161</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -5786,7 +5784,6 @@
       <c r="H161" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
